--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21417,6 +21417,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="916">
+      <c r="A916" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B916" t="n">
+        <v>0</v>
+      </c>
+      <c r="C916" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="D916" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="E916" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="G916" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B917" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C917" t="n">
+        <v>0.254000008106232</v>
+      </c>
+      <c r="D917" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E917" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G917" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21463,6 +21463,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B918" t="n">
+        <v>0</v>
+      </c>
+      <c r="C918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G918" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21486,6 +21486,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B919" t="n">
+        <v>0</v>
+      </c>
+      <c r="C919" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D919" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E919" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G919" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21350,22 +21350,22 @@
     </row>
     <row r="913">
       <c r="A913" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B913" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C913" t="n">
-        <v>0.225999996066093</v>
+        <v>0.230000004172325</v>
       </c>
       <c r="D913" t="n">
-        <v>0.225999996066093</v>
+        <v>0.230000004172325</v>
       </c>
       <c r="E913" t="n">
-        <v>0.225999996066093</v>
+        <v>0.230000004172325</v>
       </c>
       <c r="F913" t="n">
-        <v>0.225999996066093</v>
+        <v>0.230000004172325</v>
       </c>
       <c r="G913" t="s">
         <v>7</v>
@@ -21373,10 +21373,10 @@
     </row>
     <row r="914">
       <c r="A914" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B914" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="C914" t="n">
         <v>0.225999996066093</v>
@@ -21396,7 +21396,7 @@
     </row>
     <row r="915">
       <c r="A915" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B915" t="n">
         <v>0</v>
@@ -21419,7 +21419,7 @@
     </row>
     <row r="916">
       <c r="A916" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B916" t="n">
         <v>0</v>
@@ -21442,22 +21442,22 @@
     </row>
     <row r="917">
       <c r="A917" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B917" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="C917" t="n">
-        <v>0.254000008106232</v>
+        <v>0.225999996066093</v>
       </c>
       <c r="D917" t="n">
-        <v>0.23199999332428</v>
+        <v>0.225999996066093</v>
       </c>
       <c r="E917" t="n">
-        <v>0.23199999332428</v>
+        <v>0.225999996066093</v>
       </c>
       <c r="F917" t="n">
-        <v>0.238000005483627</v>
+        <v>0.225999996066093</v>
       </c>
       <c r="G917" t="s">
         <v>7</v>
@@ -21465,19 +21465,19 @@
     </row>
     <row r="918">
       <c r="A918" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B918" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="C918" t="n">
-        <v>0.238000005483627</v>
+        <v>0.254000008106232</v>
       </c>
       <c r="D918" t="n">
-        <v>0.238000005483627</v>
+        <v>0.23199999332428</v>
       </c>
       <c r="E918" t="n">
-        <v>0.238000005483627</v>
+        <v>0.23199999332428</v>
       </c>
       <c r="F918" t="n">
         <v>0.238000005483627</v>
@@ -21488,7 +21488,7 @@
     </row>
     <row r="919">
       <c r="A919" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B919" t="n">
         <v>0</v>
@@ -21506,6 +21506,29 @@
         <v>0.238000005483627</v>
       </c>
       <c r="G919" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B920" t="n">
+        <v>0</v>
+      </c>
+      <c r="C920" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D920" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E920" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F920" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G920" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21532,6 +21532,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="921">
+      <c r="A921" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B921" t="n">
+        <v>0</v>
+      </c>
+      <c r="C921" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D921" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E921" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F921" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G921" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B922" t="n">
+        <v>0</v>
+      </c>
+      <c r="C922" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D922" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E922" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G922" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21578,6 +21578,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B923" t="n">
+        <v>0</v>
+      </c>
+      <c r="C923" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D923" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E923" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F923" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G923" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21647,6 +21647,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="926">
+      <c r="A926" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B926" t="n">
+        <v>0</v>
+      </c>
+      <c r="C926" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D926" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="E926" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F926" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="G926" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21670,6 +21670,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="927">
+      <c r="A927" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B927" t="n">
+        <v>0</v>
+      </c>
+      <c r="C927" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D927" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="E927" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F927" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="G927" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21693,6 +21693,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="928">
+      <c r="A928" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B928" t="n">
+        <v>0</v>
+      </c>
+      <c r="C928" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D928" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="E928" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F928" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="G928" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21824,7 +21824,9 @@
       <c r="E933" t="n">
         <v>0.244000002741814</v>
       </c>
-      <c r="F933"/>
+      <c r="F933" t="n">
+        <v>0.244000002741814</v>
+      </c>
       <c r="G933" t="s">
         <v>7</v>
       </c>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21831,6 +21831,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="934">
+      <c r="A934" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B934" t="n">
+        <v>0</v>
+      </c>
+      <c r="C934" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D934" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E934" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G934" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21854,6 +21854,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="935">
+      <c r="A935" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B935" t="n">
+        <v>0</v>
+      </c>
+      <c r="C935" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D935" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E935" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F935" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G935" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21877,6 +21877,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B936" t="n">
+        <v>0</v>
+      </c>
+      <c r="C936" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D936" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E936" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G936" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21923,6 +21923,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="938">
+      <c r="A938" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B938" t="n">
+        <v>0</v>
+      </c>
+      <c r="C938" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D938" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E938" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G938" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21946,6 +21946,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B939" t="n">
+        <v>0</v>
+      </c>
+      <c r="C939" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D939" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E939" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G939" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -21969,6 +21969,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B940" t="n">
+        <v>0</v>
+      </c>
+      <c r="C940" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D940" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E940" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G940" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -27725,6 +27725,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B944" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C944" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D944" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E944" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G944" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H944" t="n">
+        <v>0</v>
+      </c>
+      <c r="I944" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -27754,6 +27754,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="945">
+      <c r="A945" t="s">
+        <v>9</v>
+      </c>
+      <c r="B945" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C945" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D945" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E945" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F945" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G945" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H945" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -27783,6 +27783,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" t="s">
+        <v>9</v>
+      </c>
+      <c r="B946" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C946" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D946" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E946" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F946" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G946" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H946" t="n">
+        <v>0</v>
+      </c>
+      <c r="I946" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="s">
+        <v>9</v>
+      </c>
+      <c r="B947" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C947" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="D947" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="E947" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="G947" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="H947" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I947" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -27841,6 +27841,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="s">
+        <v>9</v>
+      </c>
+      <c r="B948" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C948" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="D948" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="E948" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="F948" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="G948" t="n">
+        <v>0.24600000679493</v>
+      </c>
+      <c r="H948" t="n">
+        <v>0</v>
+      </c>
+      <c r="I948" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="s">
+        <v>9</v>
+      </c>
+      <c r="B949" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C949" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D949" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="E949" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="G949" t="n">
+        <v>0.252000004053116</v>
+      </c>
+      <c r="H949" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I949" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -27899,6 +27899,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" t="s">
+        <v>9</v>
+      </c>
+      <c r="B950" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C950" t="n">
+        <v>0.257999986410141</v>
+      </c>
+      <c r="D950" t="n">
+        <v>0.257999986410141</v>
+      </c>
+      <c r="E950" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G950" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="H950" t="n">
+        <v>48000</v>
+      </c>
+      <c r="I950" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ART.MI.xlsx
+++ b/data/ART.MI.xlsx
@@ -27928,6 +27928,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="s">
+        <v>9</v>
+      </c>
+      <c r="B951" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C951" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D951" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="E951" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G951" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="H951" t="n">
+        <v>0</v>
+      </c>
+      <c r="I951" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="s">
+        <v>9</v>
+      </c>
+      <c r="B952" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C952" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="D952" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="E952" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="G952" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="H952" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I952" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
